--- a/results/momentum_strong_2026-10-13.xlsx
+++ b/results/momentum_strong_2026-10-13.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D209"/>
+  <dimension ref="A1:D182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,29 +441,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ALISU</t>
+          <t>AGBK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AACI</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LVLU</t>
+          <t>GFUZ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ACHC</t>
+          <t>AEP</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AMBR</t>
+          <t>ALISU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -473,326 +473,274 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TBCH</t>
+          <t>JYD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AERO</t>
+          <t>BCML</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AUC</t>
+          <t>CHNR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AEHL</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>ADI</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PFAI</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BVFL</t>
+          <t>DLHC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BKHAU</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AFRI</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SIMA</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ECHO</t>
+          <t>EMPD</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BMR</t>
+          <t>ELOG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AGBK</t>
+          <t>AIRT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EMPD</t>
+          <t>LVLU</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CHNR</t>
+          <t>ENGS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AIRT</t>
+          <t>AISP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>HWKN</t>
+          <t>NTRSO</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DLXY</t>
+          <t>ENSC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AISP</t>
+          <t>ALRM</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>INSG</t>
+          <t>NXT</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ELOG</t>
+          <t>FLYE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>IRMD</t>
+          <t>OSG</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>PEBK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>AMRX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ITRN</t>
+          <t>RMCF</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FVNNU</t>
+          <t>SJ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AMPH</t>
+          <t>ANDG</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LFS</t>
+          <t>RPGL</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>GCL</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AMRX</t>
+          <t>AOUT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LMB</t>
+          <t>RSVR</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>HLP</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ANDG</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MYRG</t>
+          <t>SCHL</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>ICG</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>APEI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NTES</t>
+          <t>SNWV</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>IDAI</t>
-        </is>
-      </c>
+      <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>APEI</t>
+          <t>ARTW</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>OFLX</t>
-        </is>
-      </c>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>LSAK</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>APOG</t>
+          <t>ASO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>OMCL</t>
-        </is>
-      </c>
+      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>NCPL</t>
-        </is>
-      </c>
+      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>ATKR</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>OSW</t>
-        </is>
-      </c>
+      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>OTAI</t>
-        </is>
-      </c>
+      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ATEC</t>
+          <t>AUDC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>PWP</t>
-        </is>
-      </c>
+      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>PEBK</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AVBC</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>PWRL</t>
-        </is>
-      </c>
+      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>QQQX</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>BKHAU</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>RFAI</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BIRD</t>
+          <t>BLKB</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -812,7 +760,7 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BOW</t>
+          <t>BOLT</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -822,7 +770,7 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BPRE</t>
+          <t>BORR</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -832,7 +780,7 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BRZE</t>
+          <t>BOW</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -852,7 +800,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BSY</t>
+          <t>BSVN</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -862,7 +810,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BWMN</t>
+          <t>BSY</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -872,7 +820,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BYRN</t>
+          <t>BVFL</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -882,7 +830,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CAKE</t>
+          <t>BWIN</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -892,7 +840,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CAPNU</t>
+          <t>BZUN</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -902,7 +850,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CBC</t>
+          <t>CAKE</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -912,7 +860,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CBRL</t>
+          <t>CBC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -922,7 +870,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>CBRL</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -932,7 +880,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>CCSI</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -942,7 +890,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CFFI</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -952,7 +900,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CGNT</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -962,7 +910,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CHAD</t>
+          <t>CFFI</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -972,7 +920,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>CGNT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -982,7 +930,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CNXN</t>
+          <t>CLMB</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -992,7 +940,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>COPR</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -1002,7 +950,7 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>CLOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -1012,7 +960,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CPHC</t>
+          <t>CMRC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -1022,7 +970,7 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CRAI</t>
+          <t>CNXN</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -1032,7 +980,7 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CRCT</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -1042,7 +990,7 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -1052,7 +1000,7 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>CORT</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -1062,7 +1010,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>CRAI</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -1072,7 +1020,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>CRCT</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -1082,7 +1030,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CWCO</t>
+          <t>CRNC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -1092,7 +1040,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -1102,7 +1050,7 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -1112,7 +1060,7 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>CVSA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -1122,7 +1070,7 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DLO</t>
+          <t>DAVE</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -1132,7 +1080,7 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DMLP</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -1142,7 +1090,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -1152,7 +1100,7 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DTST</t>
+          <t>DLO</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -1162,7 +1110,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DUOL</t>
+          <t>DMLP</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -1172,7 +1120,7 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1182,7 +1130,7 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ECPG</t>
+          <t>DSGR</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1192,7 +1140,7 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1202,7 +1150,7 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EFSI</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1212,7 +1160,7 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EGBN</t>
+          <t>ECPG</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1222,7 +1170,7 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EMBC</t>
+          <t>EEIQ</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1232,7 +1180,7 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ENSC</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1242,7 +1190,7 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EVCM</t>
+          <t>EFSI</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -1252,7 +1200,7 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>EGBN</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -1262,7 +1210,7 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>EMBC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1272,7 +1220,7 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>EXEL</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1282,7 +1230,7 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>EXLS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1292,7 +1240,7 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FIRY</t>
+          <t>FIVN</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1302,7 +1250,7 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FLXS</t>
+          <t>FSBW</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1312,7 +1260,7 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FNKO</t>
+          <t>GDYN</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1322,7 +1270,7 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FOSL</t>
+          <t>GIBO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1332,7 +1280,7 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>FRAF</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1342,7 +1290,7 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1352,7 +1300,7 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FROG</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -1362,7 +1310,7 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>FSBW</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -1372,7 +1320,7 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>GOOGM</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -1382,7 +1330,7 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>GOOGN</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -1392,7 +1340,7 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GECCH</t>
+          <t>GTLB</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -1402,7 +1350,7 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GLBE</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -1412,7 +1360,7 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>HCKT</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -1422,7 +1370,7 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -1432,7 +1380,7 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>HMR</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -1442,7 +1390,7 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GOOGM</t>
+          <t>HOWL</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -1452,7 +1400,7 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GOOGN</t>
+          <t>HPK</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -1462,7 +1410,7 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GRDX</t>
+          <t>HSTM</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -1472,7 +1420,7 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -1482,7 +1430,7 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>IBEX</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -1492,7 +1440,7 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>HBIO</t>
+          <t>IBRX</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -1502,7 +1450,7 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>HCKT</t>
+          <t>ICG</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -1512,7 +1460,7 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>III</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -1522,7 +1470,7 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>IMPP</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -1532,7 +1480,7 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>INGN</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -1542,7 +1490,7 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>HYFT</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -1552,7 +1500,7 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>HYNE</t>
+          <t>IRMD</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -1562,7 +1510,7 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>IBEX</t>
+          <t>JANX</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -1572,7 +1520,7 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>JOYY</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -1582,7 +1530,7 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>INAC</t>
+          <t>KBON</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -1592,7 +1540,7 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>INGN</t>
+          <t>KFFB</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -1602,7 +1550,7 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>INTR</t>
+          <t>KGEI</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -1612,7 +1560,7 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>IRIX</t>
+          <t>KNSA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -1622,7 +1570,7 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>KROS</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -1632,7 +1580,7 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>JANX</t>
+          <t>KRSA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -1642,7 +1590,7 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>JFU</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -1652,7 +1600,7 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>JOYY</t>
+          <t>LAUR</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -1662,7 +1610,7 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>KE</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -1672,7 +1620,7 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>KGEI</t>
+          <t>LOCO</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -1682,7 +1630,7 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>KMRK</t>
+          <t>LOPE</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -1692,7 +1640,7 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>KRAQ</t>
+          <t>LYFT</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -1702,7 +1650,7 @@
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>KRNT</t>
+          <t>MANE</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -1712,7 +1660,7 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>KRSA</t>
+          <t>MCGA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -1722,7 +1670,7 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>MEOH</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -1732,7 +1680,7 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>LAUR</t>
+          <t>MESH</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -1742,7 +1690,7 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>LCUT</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -1752,7 +1700,7 @@
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>MNRO</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -1762,7 +1710,7 @@
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>MQ</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -1772,7 +1720,7 @@
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>LOPE</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -1782,7 +1730,7 @@
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>MWYN</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -1792,7 +1740,7 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>MAT</t>
+          <t>NATH</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -1802,7 +1750,7 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>MKTX</t>
+          <t>NCPL</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -1812,7 +1760,7 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>MQ</t>
+          <t>NECB</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -1822,7 +1770,7 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>NKSH</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -1832,7 +1780,7 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>MSGM</t>
+          <t>NRDS</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -1842,7 +1790,7 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>MWYN</t>
+          <t>NSIT</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -1852,7 +1800,7 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>NATH</t>
+          <t>NWE</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -1862,7 +1810,7 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>NDSN</t>
+          <t>NXTC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -1872,7 +1820,7 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>NECB</t>
+          <t>ODD</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -1882,7 +1830,7 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>NICE</t>
+          <t>OLLI</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -1892,7 +1840,7 @@
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>NKSH</t>
+          <t>OPLN</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -1902,7 +1850,7 @@
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>NMAD</t>
+          <t>OPRX</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -1912,7 +1860,7 @@
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>NNBR</t>
+          <t>PANL</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -1922,7 +1870,7 @@
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>NSIT</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -1932,7 +1880,7 @@
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>PCTY</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -1942,7 +1890,7 @@
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>NTGR</t>
+          <t>PDSB</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -1952,7 +1900,7 @@
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>NTRP</t>
+          <t>PGNY</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -1962,7 +1910,7 @@
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -1972,7 +1920,7 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>NWE</t>
+          <t>PLUS</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -1982,7 +1930,7 @@
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>NXPL</t>
+          <t>PNRG</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -1992,7 +1940,7 @@
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>OCTV</t>
+          <t>PRAA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -2002,7 +1950,7 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ODD</t>
+          <t>PRDO</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -2012,7 +1960,7 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>OLLI</t>
+          <t>PSIX</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -2022,7 +1970,7 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>OM</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -2032,7 +1980,7 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>ONBPP</t>
+          <t>PUBM</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -2042,7 +1990,7 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>PXS</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -2052,7 +2000,7 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>OPRT</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -2062,7 +2010,7 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>QDEL</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -2072,7 +2020,7 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>PAX</t>
+          <t>QLEP</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -2082,7 +2030,7 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>PBYI</t>
+          <t>QNBC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -2092,7 +2040,7 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>QTEX</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -2102,7 +2050,7 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>PCTY</t>
+          <t>RFAI</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -2112,7 +2060,7 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>PDSB</t>
+          <t>RGC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -2122,7 +2070,7 @@
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>PENG</t>
+          <t>RIGL</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -2132,7 +2080,7 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>PICS</t>
+          <t>RVSB</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -2142,7 +2090,7 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>PLUS</t>
+          <t>SAFT</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -2152,7 +2100,7 @@
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>PNRG</t>
+          <t>SAMG</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -2162,7 +2110,7 @@
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>PNTG</t>
+          <t>SCSC</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -2172,7 +2120,7 @@
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>POCI</t>
+          <t>SLDE</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -2182,7 +2130,7 @@
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>SLSN</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -2192,7 +2140,7 @@
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PRDO</t>
+          <t>SMTI</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -2202,7 +2150,7 @@
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PRHI</t>
+          <t>SMXT</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -2212,7 +2160,7 @@
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>SND</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -2222,7 +2170,7 @@
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PSIX</t>
+          <t>SNFCA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -2232,7 +2180,7 @@
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>SPSC</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -2242,7 +2190,7 @@
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PUBM</t>
+          <t>SPT</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -2252,7 +2200,7 @@
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
-          <t>QLYS</t>
+          <t>SSTI</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -2262,7 +2210,7 @@
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
-          <t>RCBC</t>
+          <t>STGW</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -2272,7 +2220,7 @@
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>RCKY</t>
+          <t>SUJA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
@@ -2282,7 +2230,7 @@
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>SUNB</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -2292,7 +2240,7 @@
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
-          <t>RDWR</t>
+          <t>SWKHL</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -2302,7 +2250,7 @@
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
-          <t>RGS</t>
+          <t>SWRD</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -2312,7 +2260,7 @@
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
-          <t>RMCF</t>
+          <t>TBCH</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -2322,7 +2270,7 @@
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
-          <t>RPD</t>
+          <t>TEAM</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -2332,7 +2280,7 @@
       <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
-          <t>RVSB</t>
+          <t>TENB</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -2342,7 +2290,7 @@
       <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
-          <t>RWAYM</t>
+          <t>TJGC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -2352,7 +2300,7 @@
       <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
-          <t>RYZ</t>
+          <t>TLN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -2362,7 +2310,7 @@
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
-          <t>SAFT</t>
+          <t>TRI</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -2372,7 +2320,7 @@
       <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
-          <t>SAMG</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
@@ -2382,7 +2330,7 @@
       <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr">
         <is>
-          <t>SCHL</t>
+          <t>WCCB</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -2392,7 +2340,7 @@
       <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
-          <t>SGC</t>
+          <t>XFLH</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
@@ -2402,281 +2350,11 @@
       <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>ZSQR</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr"/>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>SIBN</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr"/>
-      <c r="D183" t="inlineStr"/>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr"/>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>SKK</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr"/>
-      <c r="D184" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr"/>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>SKWD</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr"/>
-      <c r="D185" t="inlineStr"/>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr"/>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>SLDE</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr"/>
-      <c r="D186" t="inlineStr"/>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr"/>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>SMXT</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr"/>
-      <c r="D187" t="inlineStr"/>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr"/>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>SNPS</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr"/>
-      <c r="D188" t="inlineStr"/>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr"/>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>SOTK</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr"/>
-      <c r="D189" t="inlineStr"/>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr"/>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>SPCX</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr"/>
-      <c r="D190" t="inlineStr"/>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr"/>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>SPSC</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr"/>
-      <c r="D191" t="inlineStr"/>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr"/>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>STDN</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr"/>
-      <c r="D192" t="inlineStr"/>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr"/>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>STRA</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr"/>
-      <c r="D193" t="inlineStr"/>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr"/>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>STRC</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr"/>
-      <c r="D194" t="inlineStr"/>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr"/>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>SUNB</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr"/>
-      <c r="D195" t="inlineStr"/>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr"/>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>SVRN</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr"/>
-      <c r="D196" t="inlineStr"/>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr"/>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>SWKHL</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr"/>
-      <c r="D197" t="inlineStr"/>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr"/>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>TACH</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr"/>
-      <c r="D198" t="inlineStr"/>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr"/>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>TECH</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr"/>
-      <c r="D199" t="inlineStr"/>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr"/>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>TLN</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr"/>
-      <c r="D200" t="inlineStr"/>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr"/>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>TLSA</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr"/>
-      <c r="D201" t="inlineStr"/>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr"/>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>TPCS</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr"/>
-      <c r="D202" t="inlineStr"/>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr"/>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>TRMB</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr"/>
-      <c r="D203" t="inlineStr"/>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr"/>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>TRMD</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr"/>
-      <c r="D204" t="inlineStr"/>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr"/>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>UTHR</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr"/>
-      <c r="D205" t="inlineStr"/>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr"/>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>VAI</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr"/>
-      <c r="D206" t="inlineStr"/>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr"/>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>VCTR</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr"/>
-      <c r="D207" t="inlineStr"/>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr"/>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>VYLR</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr"/>
-      <c r="D208" t="inlineStr"/>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr"/>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>WCCB</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr"/>
-      <c r="D209" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
